--- a/Assets/Data/Fly.xlsx
+++ b/Assets/Data/Fly.xlsx
@@ -82,7 +82,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/room</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -109,7 +109,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_lie pos(650,772) h(330)</t>
+          <t xml:space="preserve">Cus_lie:pos(650,772):h(330)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -131,7 +131,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -197,36 +197,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">书中的文字有着同样的地心引力，拉着他往想象中的天空坠落。可是，一切很快被推向章节末尾。</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">Cus恋恋不舍地在书的左下角轻轻折上一个角，标记着看到了这里。</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -243,7 +223,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_stand pos(1360,1110) h(930)</t>
+          <t xml:space="preserve">Cus_stand:pos(1360,1110):h(930)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -265,7 +245,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_run pos(1500,1010) h(420)</t>
+          <t xml:space="preserve">Cus_run:pos(1500,1010):h(420)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -275,11 +255,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">推开门，熟悉的小镇模样浮现。走在有绿茵草包裹的石板路上，他问：</t>
@@ -287,17 +262,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈_stand pos(600,1120) h(980), Cus_stand pos(1300,1120) h(800)</t>
+          <t xml:space="preserve">妈妈_stand:pos(600,1120):h(980), Cus_stand:pos(1300,1120):h(800)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/street</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">street</t>
         </is>
       </c>
     </row>
@@ -348,7 +318,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈特写_smile pos(300,1040) h(640)</t>
+          <t xml:space="preserve">妈妈特写_smile:pos(300,1040):h(640)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -382,12 +352,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈_stand pos(380,910) h(760)</t>
+          <t xml:space="preserve">妈妈_stand:pos(380,910):h(760)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/ascent_slope</t>
+          <t xml:space="preserve">ascent_slope</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -429,11 +399,6 @@
           <t xml:space="preserve">“好了。”</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台词</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -453,96 +418,41 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">祖父默许后，他坐进驾驶舱，凭借在书中对滑翔机的理解，很快掌握了全部要领。这是第一次尝试起飞。</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">母亲用手遮住阳光在旁边，好像叮嘱了几句，但被风扇声所淹没。</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">没有倒数，没有仪式。他推着操纵杆，紧盯着前方上坡的边缘。风刚好从身后推过来，就跑了。九码、八码。</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">旋转的扇叶搅动地上的草。还剩五码时，地面忽然软了。还剩一码，没有一码了，地面已经看不见了。</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">他离开了地面，起初只是悬浮，沿着草尖滑行。母亲的声音在后方追着他，慢一点。</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">然后风变了，像是托举着他，像是整片天空深处一只巨大的温柔的手掌将他往上捧。草坡迅速缩小，母亲的身影变成一个小点。</t>
@@ -550,21 +460,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/ascent_cloud</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">ascent_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t xml:space="preserve">而他还在上升。云层扑面，起初像棉花糖一样柔软地擦过他的手臂，然后变薄、变透明，穿过去了。</t>
@@ -575,18 +475,8 @@
           <t xml:space="preserve">妈妈</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t xml:space="preserve">云层之上，那寂灭天空的一段布满前所未见的蓝，比所有的蓝都深，清凉，像是在缓缓流淌。再往上，紫色渐尽，露出宇宙的黑。</t>
@@ -594,55 +484,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/ascent_space</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">ascent_space</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">一切美得多么难以言传，多么安静、明丽而慷慨，浓稠地铺满整个视野。缀着的星向他眨眼，密密麻麻的，触手可及。</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">风声消失。这里没有风，没有声音，滑翔机的翼面不再震颤。这是安静的滑行。</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t xml:space="preserve">他往前漂着，回首，自己已站在了地月系的边缘。小行星挂着炫彩铺在他脚下，成了沉浮的、浩瀚的星球。</t>
@@ -650,89 +510,39 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/earth</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t xml:space="preserve">翻折。蓝紫色。青光。离散出梦幻的色彩。白色的、潮湿的月亮跳着快步穿过半球形的湖穹顶。星星默默地跟随，穿起了一道星河。</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t xml:space="preserve">好安静。</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t xml:space="preserve">他忽然想，这大概就是最高的地方。是一种很笃定的、平静的直觉。此刻这一秒，脚下这个高度是他所能达到的最远的地方。</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">还没有害怕，也没有不舍，只是张开手臂，让那片沉默的、缀满星辰的黑暗从指缝间流过，然后缓缓地开始下降。</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t xml:space="preserve">母亲在坡脚。</t>
@@ -740,17 +550,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈_stand pos(380,910) h(760)</t>
+          <t xml:space="preserve">妈妈_stand:pos(380,910):h(760)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/ascent_dusk</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">ascent_dusk</t>
         </is>
       </c>
     </row>
@@ -767,7 +572,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈特写_smile pos(300,1040) h(640)</t>
+          <t xml:space="preserve">妈妈特写_smile:pos(300,1040):h(640)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -789,17 +594,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_laugh pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_laugh:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t xml:space="preserve">妈妈特写</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台词</t>
         </is>
       </c>
     </row>
@@ -845,7 +645,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/room3</t>
+          <t xml:space="preserve">room3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -860,45 +660,20 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">想到等天晴了再说，然后天晴了，就忘了，就是这样。</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t xml:space="preserve">日子一天挨着一天，像书一样翻过去就翻过去了。偶尔翻书，感觉到纸张的毛边，也不会回头去看。</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t xml:space="preserve">有一天他在收拾房间，从柜子底下翻出一本还折着角的书。</t>
@@ -906,29 +681,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_side pos(1540,1090) h(640)</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">Cus_side:pos(1540,1090):h(640)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t xml:space="preserve">还是那本，封面旧了，那澄澈的蓝变成了泛着黄的浅绿色。</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -945,7 +705,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -960,19 +720,9 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cus</t>
-        </is>
-      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t xml:space="preserve">想不起来。</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">心声</t>
         </is>
       </c>
     </row>
@@ -996,12 +746,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_back pos(960,1010) h(430)</t>
+          <t xml:space="preserve">Cus_back:pos(960,1010):h(430)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/dream</t>
+          <t xml:space="preserve">dream</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1016,87 +766,37 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t xml:space="preserve">天空很大，大得失去了边际。蓝，不像真的。晴云没有瑕疵，像是颜料刷上去的。</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t xml:space="preserve">然后他看见了很多鸟，像迁徙的鸟群，从天空的一端飞向另一端，亦或是交错着，在天空下面。</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t xml:space="preserve">它们的姿态好像就是那样的，飞翔好像和走路一样简单。他站在地上，仰着头。</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t xml:space="preserve">风从他身边经过，却没有托住他。地面很平、很硬。他身边什么都没有。</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t xml:space="preserve">一个人坐着滑翔机飞过来，近在咫尺，触手可及。滑翔机上的人看见了他，笑了一下，挥了挥手，然后扬长而去。</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -1113,7 +813,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -1145,11 +845,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C58" t="inlineStr">
         <is>
           <t xml:space="preserve">他醒了。</t>
@@ -1157,7 +852,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/night</t>
+          <t xml:space="preserve">night</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -1165,18 +860,8 @@
           <t xml:space="preserve">Cus</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t xml:space="preserve">窗外天还没亮，但他已经完全清醒了，胸腔里堵着什么。</t>
@@ -1184,21 +869,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C60" t="inlineStr">
         <is>
           <t xml:space="preserve">小时候搭积木搭到了很高，塌了，他放声哭了出来。不是因为难过，但那个高度也不可能完全一样地出现第二次。只是想哭。</t>
@@ -1209,18 +884,8 @@
           <t xml:space="preserve">Cus特写</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t xml:space="preserve">他翻身坐起来，想了很久，奔向祖父的后院。</t>
@@ -1228,12 +893,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_run pos(1500,1010) h(420)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">Cus_run:pos(1500,1010):h(420)</t>
         </is>
       </c>
     </row>
@@ -1257,12 +917,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_side pos(420,1100) h(720)</t>
+          <t xml:space="preserve">Cus_side:pos(420,1100):h(720)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/slope</t>
+          <t xml:space="preserve">slope</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -1277,36 +937,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t xml:space="preserve">望向那架滑翔机。有一颗螺丝松动，他用手捏着发锈的边缘，转紧，凑近，表面的漆泛白，抚摸时发出粉尘摩擦的声响。</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t xml:space="preserve">母亲没有来，他没有告诉她。</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -1323,7 +963,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -1360,79 +1000,34 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t xml:space="preserve">风向变了，从背后推。九码，八码。风扇声呼啸。第七码，地面没有变软。三码，两码。</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C69" t="inlineStr">
         <is>
           <t xml:space="preserve">他拼命地拉上操纵杆，但滑翔机还在跑，轮子还在地上。风呼啦呼啦地拍在他脸上。像是一只学飞的幼鸟。又落下了。</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t xml:space="preserve">他记得飞起来应该是什么感觉。风应该是托着的，像一只手掌，温柔地把他往上捧。可现在风只是吹，抓不住的，留不下的。</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t xml:space="preserve">再试。推得更猛。第三码，第二码，地面硬邦邦的，地面震了一下。是风不对，季节不对，是他不对了。</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t xml:space="preserve">他停下来。双手握成拳，砸在膝盖上。</t>
@@ -1440,12 +1035,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_side pos(420,1100) h(720)</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">Cus_side:pos(420,1100):h(720)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1052,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -1489,7 +1079,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_side pos(420,1100) h(720)</t>
+          <t xml:space="preserve">Cus_side:pos(420,1100):h(720)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -1504,53 +1094,23 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t xml:space="preserve">他坐在草坡上很久。</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t xml:space="preserve">太阳快落下去了，天边烧成橘红色，云层被镶了一圈金边。和那天一模一样。</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t xml:space="preserve">他想起母亲，想告诉她什么——“我又去飞了，没飞起来。”然后呢？{nw}</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1148,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/slope</t>
+          <t xml:space="preserve">slope</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -1603,28 +1163,13 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t xml:space="preserve">记忆的油漆上，透过落日的光变成一片暗红。草也染成了暗绿，像被琥珀封住了，在这个夜晚。</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t xml:space="preserve">回家的路上，天彻底黑了下来，路灯一盏一盏亮起来，在脚下照出一圈阴影。他走过每一个光斑，走过一格一格的地砖。</t>
@@ -1632,68 +1177,33 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_back pos(1000,1060) h(360)</t>
+          <t xml:space="preserve">Cus_back:pos(1000,1060):h(360)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/streetnight</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">streetnight</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t xml:space="preserve">他不会再来这草坡了。他知道。来了也不会有三码后的那一下——那高度，那片安静的、缀满星辰的黑，已经永远地留在一个十几岁的夏天的傍晚。</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t xml:space="preserve">取不回来，也不可能复刻。</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t xml:space="preserve">他加快脚步，没有回头。身后的草坡在夜色里沉下去，成了一片剪影，最后朦胧进夜色中，和他所有走过再也不会回来的地方一样，安静地消失了。</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1234,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈_cook pos(1380,1100) h(640)</t>
+          <t xml:space="preserve">妈妈_cook:pos(1380,1100):h(640)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/room</t>
+          <t xml:space="preserve">room</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -1773,12 +1283,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_pout pos(1640,1040) h(660)</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台词</t>
+          <t xml:space="preserve">Cus特写_pout:pos(1640,1040):h(660)</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1356,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈特写_smile pos(300,1040) h(640)</t>
+          <t xml:space="preserve">妈妈特写_smile:pos(300,1040):h(640)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -1878,7 +1383,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈_cook pos(1380,1100) h(640)</t>
+          <t xml:space="preserve">妈妈_cook:pos(1380,1100):h(640)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -1905,7 +1410,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">妈妈特写_smile pos(300,1040) h(640)</t>
+          <t xml:space="preserve">妈妈特写_smile:pos(300,1040):h(640)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -1920,19 +1425,9 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">妈妈</t>
-        </is>
-      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t xml:space="preserve">“你擦了擦眼泪，又搭了一个，比那个矮。”</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台词</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1444,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/BG/grassnight</t>
+          <t xml:space="preserve">grassnight</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -1964,79 +1459,34 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C100" t="inlineStr">
         <is>
           <t xml:space="preserve">他的双手仿佛兜住了一小口风，把他托离地面——半米，也许不到半米。风从他张开的手指尖穿过，凉凉的，带着晚秋枯草的气味。然后他落了下来。</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t xml:space="preserve">半米。</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t xml:space="preserve">不过只是半米。他望向天空。干脆躺在草地上，就这样望着它。没有星星，路灯太亮了，把星星都盖住了。</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t xml:space="preserve">但他知道它们在那里，就在那云层的后面，那层光的后面，和之前他看到的一模一样，密密麻麻。</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
-        </is>
-      </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{clear}</t>
-        </is>
-      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t xml:space="preserve">他站了起来，拍了拍膝盖上的土。</t>
@@ -2044,12 +1494,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus_stand pos(1380,1110) h(800)</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">旁白</t>
+          <t xml:space="preserve">Cus_stand:pos(1380,1110):h(800)</t>
         </is>
       </c>
     </row>
@@ -2066,7 +1511,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cus特写_laugh pos(1640,1040) h(660)</t>
+          <t xml:space="preserve">Cus特写_laugh:pos(1640,1040):h(660)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">

--- a/Assets/Data/Fly.xlsx
+++ b/Assets/Data/Fly.xlsx
@@ -438,6 +438,11 @@
           <t xml:space="preserve">母亲在旁边用手遮住阳光，好像叮嘱了几句，但被风扇声淹没了。</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight:seg(0,3)</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">Fly/bgm_flight:vol(0.35)</t>
@@ -452,7 +457,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_roll, lock:on</t>
+          <t xml:space="preserve">se:Fly/sfx_roll, flight:seg(3,8), lock:on</t>
         </is>
       </c>
     </row>
@@ -464,7 +469,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_lift</t>
+          <t xml:space="preserve">se:Fly/sfx_lift, flight:seg(8,13.5)</t>
         </is>
       </c>
     </row>
@@ -474,6 +479,11 @@
           <t xml:space="preserve">他离开了地面，起初只是悬浮，沿着草尖滑行。母亲的声音在后方追着他：“慢一点。”</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight:seg(13.5,19)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
@@ -483,7 +493,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_swoosh</t>
+          <t xml:space="preserve">se:Fly/sfx_swoosh, flight:seg(19,24.6)</t>
         </is>
       </c>
     </row>
@@ -493,6 +503,11 @@
           <t xml:space="preserve">草坡迅速缩小，母亲的身影变成一个小点，地面光滑得像铺成一块绿色的绒布。河流变成绒布上蓝色的细线。</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight:seg(24.6,30)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="C33" t="inlineStr">
@@ -507,7 +522,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_cloud</t>
+          <t xml:space="preserve">se:Fly/sfx_cloud, flight:seg(30,38)</t>
         </is>
       </c>
     </row>
@@ -524,7 +539,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_chime</t>
+          <t xml:space="preserve">se:Fly/sfx_chime, flight:seg(38,48)</t>
         </is>
       </c>
     </row>
@@ -536,7 +551,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_shimmer</t>
+          <t xml:space="preserve">se:Fly/sfx_shimmer, flight:seg(48,54)</t>
         </is>
       </c>
     </row>
@@ -548,7 +563,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_settle</t>
+          <t xml:space="preserve">se:Fly/sfx_settle, flight:seg(54,62)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -570,7 +585,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_swoosh, show:EarthFX</t>
+          <t xml:space="preserve">se:Fly/sfx_swoosh, flight:seg(62,69)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -587,7 +602,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_bloom, play:翻折</t>
+          <t xml:space="preserve">se:Fly/sfx_bloom, flight:seg(69,74)</t>
         </is>
       </c>
     </row>
@@ -599,7 +614,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_moon</t>
+          <t xml:space="preserve">se:Fly/sfx_moon, flight:seg(74,81)</t>
         </is>
       </c>
     </row>
@@ -609,6 +624,11 @@
           <t xml:space="preserve">好安静。</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight:seg(81,84)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
@@ -616,6 +636,11 @@
           <t xml:space="preserve">他忽然想，这大概就是最高的地方。笃定的、平静的直觉。就像水往低处流一样自然，他就是知道。</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight:seg(84,90)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="C42" t="inlineStr">
@@ -625,7 +650,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">se:Fly/sfx_descend</t>
+          <t xml:space="preserve">se:Fly/sfx_descend, flight:seg(90,98)</t>
         </is>
       </c>
     </row>
@@ -642,7 +667,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">lock:off, hide:EarthFX</t>
+          <t xml:space="preserve">lock:off, flight:off</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1513,7 +1538,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fly/bgm_branchB:vol(0.35)</t>
+          <t xml:space="preserve">Fly/bgm_branchB:vol(0.35):out(6):in(4)</t>
         </is>
       </c>
     </row>
